--- a/data/삼성카드_일별_기준주가.xlsx
+++ b/data/삼성카드_일별_기준주가.xlsx
@@ -11285,25 +11285,25 @@
         <v>46283</v>
       </c>
       <c r="B419" t="n">
-        <v>44000</v>
+        <v>43750</v>
       </c>
       <c r="C419" t="n">
-        <v>71754</v>
+        <v>121864</v>
       </c>
       <c r="D419" t="n">
-        <v>46813</v>
+        <v>46774</v>
       </c>
       <c r="E419" t="n">
-        <v>46162</v>
+        <v>46105</v>
       </c>
       <c r="F419" t="n">
-        <v>44623</v>
+        <v>44470</v>
       </c>
       <c r="G419" t="n">
-        <v>45866</v>
+        <v>45783</v>
       </c>
       <c r="H419" t="n">
-        <v>-0.09941290816627069</v>
+        <v>-0.1010426279722751</v>
       </c>
     </row>
   </sheetData>

--- a/data/삼성카드_일별_기준주가.xlsx
+++ b/data/삼성카드_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H419"/>
+  <dimension ref="A1:H420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11306,6 +11306,32 @@
         <v>-0.1010426279722751</v>
       </c>
     </row>
+    <row r="420">
+      <c r="A420" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B420" t="n">
+        <v>43250</v>
+      </c>
+      <c r="C420" t="n">
+        <v>105347</v>
+      </c>
+      <c r="D420" t="n">
+        <v>46659</v>
+      </c>
+      <c r="E420" t="n">
+        <v>45952</v>
+      </c>
+      <c r="F420" t="n">
+        <v>44046</v>
+      </c>
+      <c r="G420" t="n">
+        <v>45552</v>
+      </c>
+      <c r="H420" t="n">
+        <v>-0.1055783541793477</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성카드_일별_기준주가.xlsx
+++ b/data/삼성카드_일별_기준주가.xlsx
@@ -11337,25 +11337,25 @@
         <v>46287</v>
       </c>
       <c r="B421" t="n">
-        <v>43300</v>
+        <v>42850</v>
       </c>
       <c r="C421" t="n">
-        <v>11044</v>
+        <v>153641</v>
       </c>
       <c r="D421" t="n">
-        <v>46637</v>
+        <v>46515</v>
       </c>
       <c r="E421" t="n">
-        <v>45939</v>
+        <v>45758</v>
       </c>
       <c r="F421" t="n">
-        <v>43861</v>
+        <v>43587</v>
       </c>
       <c r="G421" t="n">
-        <v>45479</v>
+        <v>45287</v>
       </c>
       <c r="H421" t="n">
-        <v>-0.1070117222014962</v>
+        <v>-0.1107816764515306</v>
       </c>
     </row>
   </sheetData>

--- a/data/삼성카드_일별_기준주가.xlsx
+++ b/data/삼성카드_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H421"/>
+  <dimension ref="A1:H422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11358,6 +11358,32 @@
         <v>-0.1107816764515306</v>
       </c>
     </row>
+    <row r="422">
+      <c r="A422" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B422" t="n">
+        <v>42450</v>
+      </c>
+      <c r="C422" t="n">
+        <v>100174</v>
+      </c>
+      <c r="D422" t="n">
+        <v>46398</v>
+      </c>
+      <c r="E422" t="n">
+        <v>45628</v>
+      </c>
+      <c r="F422" t="n">
+        <v>43271</v>
+      </c>
+      <c r="G422" t="n">
+        <v>45099</v>
+      </c>
+      <c r="H422" t="n">
+        <v>-0.1144730899880225</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성카드_일별_기준주가.xlsx
+++ b/data/삼성카드_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H422"/>
+  <dimension ref="A1:H423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11384,6 +11384,32 @@
         <v>-0.1144730899880225</v>
       </c>
     </row>
+    <row r="423">
+      <c r="A423" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B423" t="n">
+        <v>43350</v>
+      </c>
+      <c r="C423" t="n">
+        <v>163636</v>
+      </c>
+      <c r="D423" t="n">
+        <v>46115</v>
+      </c>
+      <c r="E423" t="n">
+        <v>45299</v>
+      </c>
+      <c r="F423" t="n">
+        <v>43150</v>
+      </c>
+      <c r="G423" t="n">
+        <v>44855</v>
+      </c>
+      <c r="H423" t="n">
+        <v>-0.1192640735141078</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성카드_일별_기준주가.xlsx
+++ b/data/삼성카드_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H423"/>
+  <dimension ref="A1:H424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11410,6 +11410,32 @@
         <v>-0.1192640735141078</v>
       </c>
     </row>
+    <row r="424">
+      <c r="A424" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B424" t="n">
+        <v>42500</v>
+      </c>
+      <c r="C424" t="n">
+        <v>80255</v>
+      </c>
+      <c r="D424" t="n">
+        <v>46010</v>
+      </c>
+      <c r="E424" t="n">
+        <v>45205</v>
+      </c>
+      <c r="F424" t="n">
+        <v>42943</v>
+      </c>
+      <c r="G424" t="n">
+        <v>44719</v>
+      </c>
+      <c r="H424" t="n">
+        <v>-0.1219344577745489</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성카드_일별_기준주가.xlsx
+++ b/data/삼성카드_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H424"/>
+  <dimension ref="A1:H425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11436,6 +11436,32 @@
         <v>-0.1219344577745489</v>
       </c>
     </row>
+    <row r="425">
+      <c r="A425" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B425" t="n">
+        <v>42200</v>
+      </c>
+      <c r="C425" t="n">
+        <v>100571</v>
+      </c>
+      <c r="D425" t="n">
+        <v>45840</v>
+      </c>
+      <c r="E425" t="n">
+        <v>44550</v>
+      </c>
+      <c r="F425" t="n">
+        <v>42764</v>
+      </c>
+      <c r="G425" t="n">
+        <v>44384</v>
+      </c>
+      <c r="H425" t="n">
+        <v>-0.1285122425337234</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성카드_일별_기준주가.xlsx
+++ b/data/삼성카드_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H425"/>
+  <dimension ref="A1:H427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11462,6 +11462,58 @@
         <v>-0.1285122425337234</v>
       </c>
     </row>
+    <row r="426">
+      <c r="A426" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B426" t="n">
+        <v>41850</v>
+      </c>
+      <c r="C426" t="n">
+        <v>68537</v>
+      </c>
+      <c r="D426" t="n">
+        <v>45775</v>
+      </c>
+      <c r="E426" t="n">
+        <v>44333</v>
+      </c>
+      <c r="F426" t="n">
+        <v>42616</v>
+      </c>
+      <c r="G426" t="n">
+        <v>44241</v>
+      </c>
+      <c r="H426" t="n">
+        <v>-0.1313200730428636</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B427" t="n">
+        <v>41950</v>
+      </c>
+      <c r="C427" t="n">
+        <v>42214</v>
+      </c>
+      <c r="D427" t="n">
+        <v>45737</v>
+      </c>
+      <c r="E427" t="n">
+        <v>44227</v>
+      </c>
+      <c r="F427" t="n">
+        <v>42590</v>
+      </c>
+      <c r="G427" t="n">
+        <v>44185</v>
+      </c>
+      <c r="H427" t="n">
+        <v>-0.1324196430324569</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성카드_일별_기준주가.xlsx
+++ b/data/삼성카드_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H427"/>
+  <dimension ref="A1:H428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11514,6 +11514,32 @@
         <v>-0.1324196430324569</v>
       </c>
     </row>
+    <row r="428">
+      <c r="A428" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B428" t="n">
+        <v>41650</v>
+      </c>
+      <c r="C428" t="n">
+        <v>57227</v>
+      </c>
+      <c r="D428" t="n">
+        <v>45585</v>
+      </c>
+      <c r="E428" t="n">
+        <v>43857</v>
+      </c>
+      <c r="F428" t="n">
+        <v>42080</v>
+      </c>
+      <c r="G428" t="n">
+        <v>43841</v>
+      </c>
+      <c r="H428" t="n">
+        <v>-0.1391741443971019</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성카드_일별_기준주가.xlsx
+++ b/data/삼성카드_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H428"/>
+  <dimension ref="A1:H429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11540,6 +11540,32 @@
         <v>-0.1391741443971019</v>
       </c>
     </row>
+    <row r="429">
+      <c r="A429" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B429" t="n">
+        <v>41750</v>
+      </c>
+      <c r="C429" t="n">
+        <v>64480</v>
+      </c>
+      <c r="D429" t="n">
+        <v>45498</v>
+      </c>
+      <c r="E429" t="n">
+        <v>43666</v>
+      </c>
+      <c r="F429" t="n">
+        <v>41915</v>
+      </c>
+      <c r="G429" t="n">
+        <v>43693</v>
+      </c>
+      <c r="H429" t="n">
+        <v>-0.14208015079817</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성카드_일별_기준주가.xlsx
+++ b/data/삼성카드_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H429"/>
+  <dimension ref="A1:H430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11566,6 +11566,32 @@
         <v>-0.14208015079817</v>
       </c>
     </row>
+    <row r="430">
+      <c r="A430" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B430" t="n">
+        <v>41200</v>
+      </c>
+      <c r="C430" t="n">
+        <v>69429</v>
+      </c>
+      <c r="D430" t="n">
+        <v>45424</v>
+      </c>
+      <c r="E430" t="n">
+        <v>43487</v>
+      </c>
+      <c r="F430" t="n">
+        <v>41655</v>
+      </c>
+      <c r="G430" t="n">
+        <v>43522</v>
+      </c>
+      <c r="H430" t="n">
+        <v>-0.1454377663021068</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성카드_일별_기준주가.xlsx
+++ b/data/삼성카드_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H430"/>
+  <dimension ref="A1:H431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11592,6 +11592,32 @@
         <v>-0.1454377663021068</v>
       </c>
     </row>
+    <row r="431">
+      <c r="A431" s="1" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B431" t="n">
+        <v>41900</v>
+      </c>
+      <c r="C431" t="n">
+        <v>64897</v>
+      </c>
+      <c r="D431" t="n">
+        <v>45272</v>
+      </c>
+      <c r="E431" t="n">
+        <v>42999</v>
+      </c>
+      <c r="F431" t="n">
+        <v>41664</v>
+      </c>
+      <c r="G431" t="n">
+        <v>43312</v>
+      </c>
+      <c r="H431" t="n">
+        <v>-0.149561153763082</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성카드_일별_기준주가.xlsx
+++ b/data/삼성카드_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H431"/>
+  <dimension ref="A1:H432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11618,6 +11618,32 @@
         <v>-0.149561153763082</v>
       </c>
     </row>
+    <row r="432">
+      <c r="A432" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B432" t="n">
+        <v>42700</v>
+      </c>
+      <c r="C432" t="n">
+        <v>121422</v>
+      </c>
+      <c r="D432" t="n">
+        <v>45110</v>
+      </c>
+      <c r="E432" t="n">
+        <v>42976</v>
+      </c>
+      <c r="F432" t="n">
+        <v>41965</v>
+      </c>
+      <c r="G432" t="n">
+        <v>43351</v>
+      </c>
+      <c r="H432" t="n">
+        <v>-0.1487953818060437</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성카드_일별_기준주가.xlsx
+++ b/data/삼성카드_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H432"/>
+  <dimension ref="A1:H433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11644,6 +11644,32 @@
         <v>-0.1487953818060437</v>
       </c>
     </row>
+    <row r="433">
+      <c r="A433" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B433" t="n">
+        <v>42050</v>
+      </c>
+      <c r="C433" t="n">
+        <v>107465</v>
+      </c>
+      <c r="D433" t="n">
+        <v>44894</v>
+      </c>
+      <c r="E433" t="n">
+        <v>42823</v>
+      </c>
+      <c r="F433" t="n">
+        <v>42029</v>
+      </c>
+      <c r="G433" t="n">
+        <v>43248</v>
+      </c>
+      <c r="H433" t="n">
+        <v>-0.1508178051797601</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성카드_일별_기준주가.xlsx
+++ b/data/삼성카드_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H433"/>
+  <dimension ref="A1:H434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11670,6 +11670,32 @@
         <v>-0.1508178051797601</v>
       </c>
     </row>
+    <row r="434">
+      <c r="A434" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B434" t="n">
+        <v>42200</v>
+      </c>
+      <c r="C434" t="n">
+        <v>125253</v>
+      </c>
+      <c r="D434" t="n">
+        <v>44808</v>
+      </c>
+      <c r="E434" t="n">
+        <v>42699</v>
+      </c>
+      <c r="F434" t="n">
+        <v>42109</v>
+      </c>
+      <c r="G434" t="n">
+        <v>43206</v>
+      </c>
+      <c r="H434" t="n">
+        <v>-0.1516424826719551</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성카드_일별_기준주가.xlsx
+++ b/data/삼성카드_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H434"/>
+  <dimension ref="A1:H435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11696,6 +11696,32 @@
         <v>-0.1516424826719551</v>
       </c>
     </row>
+    <row r="435">
+      <c r="A435" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B435" t="n">
+        <v>42750</v>
+      </c>
+      <c r="C435" t="n">
+        <v>83164</v>
+      </c>
+      <c r="D435" t="n">
+        <v>44766</v>
+      </c>
+      <c r="E435" t="n">
+        <v>42623</v>
+      </c>
+      <c r="F435" t="n">
+        <v>42341</v>
+      </c>
+      <c r="G435" t="n">
+        <v>43243</v>
+      </c>
+      <c r="H435" t="n">
+        <v>-0.150915981071688</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성카드_일별_기준주가.xlsx
+++ b/data/삼성카드_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H435"/>
+  <dimension ref="A1:H436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11722,6 +11722,32 @@
         <v>-0.150915981071688</v>
       </c>
     </row>
+    <row r="436">
+      <c r="A436" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B436" t="n">
+        <v>42800</v>
+      </c>
+      <c r="C436" t="n">
+        <v>50057</v>
+      </c>
+      <c r="D436" t="n">
+        <v>44637</v>
+      </c>
+      <c r="E436" t="n">
+        <v>42447</v>
+      </c>
+      <c r="F436" t="n">
+        <v>42447</v>
+      </c>
+      <c r="G436" t="n">
+        <v>43177</v>
+      </c>
+      <c r="H436" t="n">
+        <v>-0.1522119028451373</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성카드_일별_기준주가.xlsx
+++ b/data/삼성카드_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H436"/>
+  <dimension ref="A1:H437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11748,6 +11748,32 @@
         <v>-0.1522119028451373</v>
       </c>
     </row>
+    <row r="437">
+      <c r="A437" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B437" t="n">
+        <v>42800</v>
+      </c>
+      <c r="C437" t="n">
+        <v>69798</v>
+      </c>
+      <c r="D437" t="n">
+        <v>44562</v>
+      </c>
+      <c r="E437" t="n">
+        <v>42462</v>
+      </c>
+      <c r="F437" t="n">
+        <v>42433</v>
+      </c>
+      <c r="G437" t="n">
+        <v>43152</v>
+      </c>
+      <c r="H437" t="n">
+        <v>-0.1527027823047772</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성카드_일별_기준주가.xlsx
+++ b/data/삼성카드_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H437"/>
+  <dimension ref="A1:H438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11774,6 +11774,32 @@
         <v>-0.1527027823047772</v>
       </c>
     </row>
+    <row r="438">
+      <c r="A438" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B438" t="n">
+        <v>42100</v>
+      </c>
+      <c r="C438" t="n">
+        <v>64630</v>
+      </c>
+      <c r="D438" t="n">
+        <v>44499</v>
+      </c>
+      <c r="E438" t="n">
+        <v>42395</v>
+      </c>
+      <c r="F438" t="n">
+        <v>42483</v>
+      </c>
+      <c r="G438" t="n">
+        <v>43125</v>
+      </c>
+      <c r="H438" t="n">
+        <v>-0.1532329321211883</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성카드_일별_기준주가.xlsx
+++ b/data/삼성카드_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H438"/>
+  <dimension ref="A1:H439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11800,6 +11800,32 @@
         <v>-0.1532329321211883</v>
       </c>
     </row>
+    <row r="439">
+      <c r="A439" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B439" t="n">
+        <v>41750</v>
+      </c>
+      <c r="C439" t="n">
+        <v>55240</v>
+      </c>
+      <c r="D439" t="n">
+        <v>44460</v>
+      </c>
+      <c r="E439" t="n">
+        <v>42324</v>
+      </c>
+      <c r="F439" t="n">
+        <v>42467</v>
+      </c>
+      <c r="G439" t="n">
+        <v>43084</v>
+      </c>
+      <c r="H439" t="n">
+        <v>-0.1540379744349978</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성카드_일별_기준주가.xlsx
+++ b/data/삼성카드_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H439"/>
+  <dimension ref="A1:H440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11826,6 +11826,32 @@
         <v>-0.1540379744349978</v>
       </c>
     </row>
+    <row r="440">
+      <c r="A440" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B440" t="n">
+        <v>42150</v>
+      </c>
+      <c r="C440" t="n">
+        <v>100262</v>
+      </c>
+      <c r="D440" t="n">
+        <v>44403</v>
+      </c>
+      <c r="E440" t="n">
+        <v>42304</v>
+      </c>
+      <c r="F440" t="n">
+        <v>42305</v>
+      </c>
+      <c r="G440" t="n">
+        <v>43004</v>
+      </c>
+      <c r="H440" t="n">
+        <v>-0.1556087887058454</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성카드_일별_기준주가.xlsx
+++ b/data/삼성카드_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H440"/>
+  <dimension ref="A1:H441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11852,6 +11852,32 @@
         <v>-0.1556087887058454</v>
       </c>
     </row>
+    <row r="441">
+      <c r="A441" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B441" t="n">
+        <v>41550</v>
+      </c>
+      <c r="C441" t="n">
+        <v>59904</v>
+      </c>
+      <c r="D441" t="n">
+        <v>44250</v>
+      </c>
+      <c r="E441" t="n">
+        <v>42274</v>
+      </c>
+      <c r="F441" t="n">
+        <v>42105</v>
+      </c>
+      <c r="G441" t="n">
+        <v>42876</v>
+      </c>
+      <c r="H441" t="n">
+        <v>-0.1581220915392016</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성카드_일별_기준주가.xlsx
+++ b/data/삼성카드_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H441"/>
+  <dimension ref="A1:H442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11878,6 +11878,32 @@
         <v>-0.1581220915392016</v>
       </c>
     </row>
+    <row r="442">
+      <c r="A442" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B442" t="n">
+        <v>40750</v>
+      </c>
+      <c r="C442" t="n">
+        <v>125005</v>
+      </c>
+      <c r="D442" t="n">
+        <v>44097</v>
+      </c>
+      <c r="E442" t="n">
+        <v>42161</v>
+      </c>
+      <c r="F442" t="n">
+        <v>41567</v>
+      </c>
+      <c r="G442" t="n">
+        <v>42608</v>
+      </c>
+      <c r="H442" t="n">
+        <v>-0.1633843193465413</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성카드_일별_기준주가.xlsx
+++ b/data/삼성카드_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H442"/>
+  <dimension ref="A1:H443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11904,6 +11904,32 @@
         <v>-0.1633843193465413</v>
       </c>
     </row>
+    <row r="443">
+      <c r="A443" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B443" t="n">
+        <v>40850</v>
+      </c>
+      <c r="C443" t="n">
+        <v>102101</v>
+      </c>
+      <c r="D443" t="n">
+        <v>43931</v>
+      </c>
+      <c r="E443" t="n">
+        <v>41957</v>
+      </c>
+      <c r="F443" t="n">
+        <v>41323</v>
+      </c>
+      <c r="G443" t="n">
+        <v>42404</v>
+      </c>
+      <c r="H443" t="n">
+        <v>-0.1673898957372028</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성카드_일별_기준주가.xlsx
+++ b/data/삼성카드_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H443"/>
+  <dimension ref="A1:H444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11930,6 +11930,32 @@
         <v>-0.1673898957372028</v>
       </c>
     </row>
+    <row r="444">
+      <c r="A444" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B444" t="n">
+        <v>41000</v>
+      </c>
+      <c r="C444" t="n">
+        <v>114726</v>
+      </c>
+      <c r="D444" t="n">
+        <v>43848</v>
+      </c>
+      <c r="E444" t="n">
+        <v>41864</v>
+      </c>
+      <c r="F444" t="n">
+        <v>41203</v>
+      </c>
+      <c r="G444" t="n">
+        <v>42305</v>
+      </c>
+      <c r="H444" t="n">
+        <v>-0.1693337783973767</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성카드_일별_기준주가.xlsx
+++ b/data/삼성카드_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H444"/>
+  <dimension ref="A1:H445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11956,6 +11956,32 @@
         <v>-0.1693337783973767</v>
       </c>
     </row>
+    <row r="445">
+      <c r="A445" s="1" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B445" t="n">
+        <v>42450</v>
+      </c>
+      <c r="C445" t="n">
+        <v>79572</v>
+      </c>
+      <c r="D445" t="n">
+        <v>43821</v>
+      </c>
+      <c r="E445" t="n">
+        <v>41872</v>
+      </c>
+      <c r="F445" t="n">
+        <v>41211</v>
+      </c>
+      <c r="G445" t="n">
+        <v>42301</v>
+      </c>
+      <c r="H445" t="n">
+        <v>-0.1694123191109191</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
